--- a/源数据.xlsx
+++ b/源数据.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27660" windowHeight="11480" activeTab="1"/>
+    <workbookView windowWidth="26000" windowHeight="10200" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="存货采购入库单" sheetId="2" r:id="rId1"/>
@@ -19803,6 +19803,7 @@
   <cols>
     <col min="1" max="1" width="21.6346153846154" customWidth="1"/>
     <col min="2" max="2" width="24.9038461538462" customWidth="1"/>
+    <col min="3" max="3" width="24.5192307692308" customWidth="1"/>
     <col min="5" max="5" width="19.3269230769231" customWidth="1"/>
   </cols>
   <sheetData>
